--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPI_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPI_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPI" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_ESPERADOS" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPI_2026_T1_Chubut_CON_ERRORES.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chubut_con_errores/MPI_2026_T1_Chubut_CON_ERRORES.xlsx
@@ -1486,7 +1486,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="6" t="n">
-        <v>45632</v>
+        <v>45633</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="BJ4" s="6" t="n">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="BJ5" s="6" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="BJ6" s="6" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="BJ7" s="6" t="n">
-        <v>45597</v>
+        <v>45598</v>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="6" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="BJ8" s="6" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="BJ9" s="6" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="6" t="n">
-        <v>45667</v>
+        <v>45668</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="BJ10" s="6" t="n">
-        <v>45601</v>
+        <v>45602</v>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="BJ11" s="6" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="6" t="n">
-        <v>45970</v>
+        <v>45971</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="BJ12" s="6" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="n">
-        <v>45756</v>
+        <v>45757</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="BJ13" s="6" t="n">
-        <v>45697</v>
+        <v>45698</v>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         </is>
       </c>
       <c r="BJ14" s="6" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="BK14" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="n">
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="BJ15" s="6" t="n">
-        <v>45620</v>
+        <v>45621</v>
       </c>
       <c r="BK15" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="6" t="n">
-        <v>45810</v>
+        <v>45811</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="BJ16" s="6" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="BK16" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         </is>
       </c>
       <c r="BJ17" s="6" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="BK17" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="6" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="BJ18" s="6" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="BK18" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         </is>
       </c>
       <c r="BJ19" s="6" t="n">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="BK19" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="6" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="BJ20" s="6" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="BK20" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         </is>
       </c>
       <c r="BJ21" s="6" t="n">
-        <v>45940</v>
+        <v>45941</v>
       </c>
       <c r="BK21" t="inlineStr">
         <is>
@@ -7025,7 +7025,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>45596</v>
+        <v>45597</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="BJ22" s="6" t="n">
-        <v>45593</v>
+        <v>45594</v>
       </c>
       <c r="BK22" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>45933</v>
+        <v>45934</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         </is>
       </c>
       <c r="BJ23" s="6" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="BK23" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="BJ24" s="6" t="n">
-        <v>45822</v>
+        <v>45823</v>
       </c>
       <c r="BK24" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>45685</v>
+        <v>45686</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="BJ25" s="6" t="n">
-        <v>45684</v>
+        <v>45685</v>
       </c>
       <c r="BK25" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="BJ26" s="6" t="n">
-        <v>45846</v>
+        <v>45847</v>
       </c>
       <c r="BK26" t="inlineStr">
         <is>
@@ -8570,7 +8570,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="BJ27" s="6" t="n">
-        <v>45650</v>
+        <v>45651</v>
       </c>
       <c r="BK27" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>46102</v>
+        <v>46103</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="BJ28" s="6" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="BK28" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="BJ29" s="6" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="BK29" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="BJ30" s="6" t="n">
-        <v>45773</v>
+        <v>45774</v>
       </c>
       <c r="BK30" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="BJ31" s="6" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="BK31" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="BJ32" s="6" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="BK32" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         </is>
       </c>
       <c r="BJ33" s="6" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="BK33" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         </is>
       </c>
       <c r="BJ34" s="6" t="n">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="BK34" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>46080</v>
+        <v>46081</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="BJ35" s="6" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="BK35" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>999</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="BJ36" s="6" t="n">
-        <v>46082</v>
+        <v>46083</v>
       </c>
       <c r="BK36" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
     <row r="38">
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="6" t="n">
-        <v>45824</v>
+        <v>45825</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         </is>
       </c>
       <c r="BJ38" s="6" t="n">
-        <v>45756</v>
+        <v>45757</v>
       </c>
       <c r="BK38" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>999</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="BJ39" s="6" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="BK39" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>999</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="BJ40" s="6" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="BK40" t="inlineStr">
         <is>
